--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5</v>
+        <v>0.7184466019417476</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="D2">
-        <v>0.3333333333333333</v>
+        <v>0.3934426229508197</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7184466019417476</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="C2">
-        <v>0.6571428571428571</v>
+        <v>0.7122302158273381</v>
       </c>
       <c r="D2">
-        <v>0.3934426229508197</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="E2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
